--- a/04_DESIGN_TABLES/DesignTable_0403.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0403.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-04-04 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-04-04</t>
+          <t>BUILD 2026-09-25: OMi 0403-04-04 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-04-04 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.5~0.50; D2@BORE=0.254~0.254; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-06-06 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-06-06</t>
+          <t>BUILD 2026-09-25: OMi 0403-06-06 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-06-06 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.63~0.625; D2@BORE=0.379~0.379; D@BORE=0.3~0.297</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-08-08 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-08-08</t>
+          <t>BUILD 2026-09-25: OMi 0403-08-08 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-08-08 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.81~0.813; D2@BORE=0.504~0.504; D@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-10-10 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-10-10</t>
+          <t>BUILD 2026-09-25: OMi 0403-10-10 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-10-10 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.94~0.938; D2@BORE=0.631~0.631; D@BORE=0.48~0.484</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="C23" t="n">
         <v>0.25</v>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34</t>
+          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16</t>
+          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_0403.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0403.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="C23" t="n">
         <v>0.25</v>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19]</t>
+          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19]; L3@DRIVE: Air-Way 1.33 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016)</t>
+          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016) | 2026-10-20 Air-Way first: L3@DRIVE OMi/Brennan 1.32 -&gt; Air-Way 1.33</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
